--- a/Supporting Files Examples/VI & Jio Numbers with Mobile Details.xlsx
+++ b/Supporting Files Examples/VI & Jio Numbers with Mobile Details.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jairaj\0_OCSPL\OD_BACKUP\Study_and_Practice\VS_Code_Practice\Asset_Management_System_v4-0\Supporting Files Examples\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ocspl12-my.sharepoint.com/personal/jairaj_b_ocspl_com/Documents/IT_Jairaj_Backup/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="939" documentId="8_{4C3387D3-3AB2-45AD-9158-1E185FD8F2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04DB4FF9-E8DB-47FA-8F8C-EA3193BF4C12}"/>
+  <xr:revisionPtr revIDLastSave="945" documentId="8_{4C3387D3-3AB2-45AD-9158-1E185FD8F2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25451FD3-CA8B-4126-8306-D3DFB486E61F}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="2" xr2:uid="{670E0C62-DBED-4E1F-A178-47152C2D6483}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{670E0C62-DBED-4E1F-A178-47152C2D6483}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -108,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1924" uniqueCount="964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1928" uniqueCount="966">
   <si>
     <t>Mobile Number</t>
   </si>
@@ -3000,6 +3000,12 @@
   </si>
   <si>
     <t>FF040100090200526420AS06153</t>
+  </si>
+  <si>
+    <t>359926420828884</t>
+  </si>
+  <si>
+    <t>359926425828889</t>
   </si>
 </sst>
 </file>
@@ -4553,6 +4559,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCC1C891-71BC-4F94-BBC0-AA0F08188826}" name="SIMTypes01" displayName="SIMTypes01" ref="A1:A17" totalsRowShown="0" headerRowDxfId="63" dataDxfId="62">
   <autoFilter ref="A1:A17" xr:uid="{BCC1C891-71BC-4F94-BBC0-AA0F08188826}"/>
@@ -12771,7 +12781,7 @@
       <formula>$M2-TODAY()&lt;=1</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
+  <dataValidations disablePrompts="1" count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Enter Mobile Expiry Date in" prompt="Enter Mobile Expiry Date in_x000a_dd-MM-YYYY format._x000a__x000a_Select NA if it's Not Applicable" sqref="M2:M57" xr:uid="{0BBD8984-7231-4DDB-95FC-3152A48C4D34}">
       <formula1>"NA"</formula1>
     </dataValidation>
@@ -13828,11 +13838,11 @@
         <v>9022930354</v>
       </c>
       <c r="C20" s="8">
-        <v>0</v>
+        <v>721</v>
       </c>
       <c r="D20" s="1" t="str">
         <f>IF(JiO_SIM_Mobile[[#This Row],[Employee Code]]=0,"-",IFERROR(IF(INDEX('EMP Info'!$B:$B, MATCH(TEXT(JiO_SIM_Mobile[[#This Row],[Employee Code]],"00000"), 'EMP Info'!$A:$A, 0))=0,"",INDEX('EMP Info'!$B:$B, MATCH(TEXT(JiO_SIM_Mobile[[#This Row],[Employee Code]],"00000"), 'EMP Info'!$A:$A, 0))),IFERROR(VLOOKUP(TEXT(JiO_SIM_Mobile[[#This Row],[Employee Code]],"00000"), 'EMP Info'!$A:$D, 2, FALSE) &amp; " (" &amp; VLOOKUP(TEXT(JiO_SIM_Mobile[[#This Row],[Employee Code]],"00000"), 'EMP Info'!$A:$D,4, FALSE) &amp; ")","")))</f>
-        <v>-</v>
+        <v>Sunil Sanjay Chanmal</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>71</v>
@@ -13847,7 +13857,7 @@
         <v>903</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>806</v>
+        <v>755</v>
       </c>
       <c r="K20" s="5">
         <v>45525</v>
@@ -13860,9 +13870,18 @@
         <f>IFERROR(IF(JiO_SIM_Mobile[[#This Row],[Purchase Date]]="","NA",EDATE(JiO_SIM_Mobile[[#This Row],[Purchase Date]],12)),"NA")</f>
         <v>45890</v>
       </c>
-      <c r="O20" s="6"/>
-      <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
+      <c r="O20" s="6" t="s">
+        <v>964</v>
+      </c>
+      <c r="P20" s="6" t="s">
+        <v>965</v>
+      </c>
+      <c r="Q20" s="6" t="s">
+        <v>908</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="S20" s="6"/>
       <c r="T20" s="6"/>
       <c r="U20" s="1" t="s">
